--- a/InputData/elec/LFHVM/Load Factor Hourly Variance Multiplier.xlsx
+++ b/InputData/elec/LFHVM/Load Factor Hourly Variance Multiplier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\elec\LFHVM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\LFHVM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BCD82B-854C-4C9D-B0F7-D4DF5E217A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89216D66-5C2B-4A02-B2AF-B276BAAFAA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25425" yWindow="2115" windowWidth="23160" windowHeight="13560" activeTab="1" xr2:uid="{E755D2B6-154D-4132-AE62-7719D42AA9EA}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{E755D2B6-154D-4132-AE62-7719D42AA9EA}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -84,18 +84,6 @@
     <t>One way to calibrate this is to try to match the EPS's peak hourly load to</t>
   </si>
   <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>Summer</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
     <t>transportation sector</t>
   </si>
   <si>
@@ -123,16 +111,28 @@
     <t>Units: dimensionless</t>
   </si>
   <si>
-    <t>Summer Peak</t>
-  </si>
-  <si>
-    <t>Winter Peak</t>
-  </si>
-  <si>
     <t>In the US, we calibrate by comparing load values to historical data from EIA's</t>
   </si>
   <si>
     <t>Form 930.</t>
+  </si>
+  <si>
+    <t>Representative Day 1</t>
+  </si>
+  <si>
+    <t>Representative Day 2</t>
+  </si>
+  <si>
+    <t>Representative Day 3</t>
+  </si>
+  <si>
+    <t>Representative Day 4</t>
+  </si>
+  <si>
+    <t>Net Peak Summer Day</t>
+  </si>
+  <si>
+    <t>Net Peak Winter Day</t>
   </si>
 </sst>
 </file>
@@ -615,12 +615,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -646,36 +646,36 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
